--- a/endowment/output/FY26_Endowment_Data_Top50.xlsx
+++ b/endowment/output/FY26_Endowment_Data_Top50.xlsx
@@ -871,15 +871,11 @@
       <c r="E7" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F7" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>12.5</v>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="6" t="n">
@@ -895,7 +891,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>FY26: Stanford Report (Sept 2026), 31.7% return, Merged Pool $61.5B as of 8/31/26 (Stanford FYE = Aug 31, not June 30). FY25 return 14.3%.</t>
+          <t>FY26: Stanford Report (Sept 2026), 31.7% return, Merged Pool $61.5B as of 8/31/26 (Stanford FYE = Aug 31, not June 30). FY25 return 14.3%. FY26 5-yr annualized 10.3%, 10-yr annualized 12.5% (Stanford Report, Sept 2026).</t>
         </is>
       </c>
     </row>
@@ -1950,10 +1946,8 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="G27" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="6" t="n">
@@ -1969,7 +1963,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>FY26: Cavalier Daily (Sept 19, 2026), UVIMCO 27% return vs. 9.8% benchmark, $15.5B→$18.8B.</t>
+          <t>FY26: Cavalier Daily (Sept 19, 2026), UVIMCO 27% return vs. 9.8% benchmark, $15.5B→$18.8B. 10-yr annualized approximately 12% ('approximately 12 percent annually' over the past 10 years), per UVIMCO CEO/CIO Robert Durden at the Sept 2026 Finance Committee meeting (Cavalier Daily); stated as an approximate figure, not to a decimal. No FY26 5-yr figure reported yet.</t>
         </is>
       </c>
     </row>
@@ -1995,15 +1989,11 @@
       <c r="E28" s="8" t="n">
         <v>37.8</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F28" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>13.5</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>18.9</v>
@@ -2021,7 +2011,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>FY26: Bloomberg (Sept 19, 2026), 37.8% return, UNC Investment Fund $12.5B→$17.0B, driven by legacy SpaceX stake. (UNC-CH Foundation portion: $6.04B→$8.16B.)</t>
+          <t>FY26: Bloomberg (Sept 19, 2026), 37.8% return, UNC Investment Fund $12.5B→$17.0B, driven by legacy SpaceX stake (about half of FY26 growth, per UNC Management Company president Stefan Strein). (UNC-CH Foundation portion: $6.04B→$8.16B.) 5-yr annualized 12.5%, 10-yr annualized 13.5% (Bloomberg/WRAL/Investing.com/Hoodline, Sept 19-22, 2026).</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3359,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>As of 2026-09-28: 6 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), University of Virginia (27.0%), Northeastern University (16.0%, management estimate). 5-year annualized: 0 of 51. 10-year annualized: 0 of 51.</t>
+          <t>As of 2026-09-28: 6 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), University of Virginia (27.0%), Northeastern University (16.0%, management estimate). 5-year annualized: 2 of 51. 10-year annualized: 3 of 51.</t>
         </is>
       </c>
     </row>

--- a/endowment/output/FY26_Endowment_Data_Top50.xlsx
+++ b/endowment/output/FY26_Endowment_Data_Top50.xlsx
@@ -99,6 +99,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -107,9 +110,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -598,38 +598,32 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="6" t="n">
+      <c r="E2" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" s="7" t="n">
         <v>27400</v>
       </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>FY25: MIT News (Oct 2025), $27.4B. FY26 not yet released.</t>
+      <c r="J2" s="7" t="n">
+        <v>29200</v>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>FY25: MIT News (Oct 2025), $27.4B. FY26: MIT News 'MIT releases financials and endowment figures for 2026' (Oct 2, 2026): pooled investments returned 10.3%; 10-yr annualized 11.7%; endowment funds $29.2B excluding pledges. 5-yr not stated.</t>
         </is>
       </c>
     </row>
@@ -652,36 +646,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="6" t="n">
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="7" t="n">
         <v>36400</v>
       </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>FY25: Princeton Alumni Weekly (Oct 2025), 11% FY25 return, $36.4B. FY26 not yet released.</t>
         </is>
@@ -706,36 +700,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="6" t="n">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="7" t="n">
         <v>56900</v>
       </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>FY25: Harvard Magazine (Oct 2025), 11.9% FY25 return, $56.9B. FY26 not yet released.</t>
         </is>
@@ -760,36 +754,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="6" t="n">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="7" t="n">
         <v>44100</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>FY25: Yale News (Oct 2025), 11.1% FY25 return, $44.1B. FY26 not yet released.</t>
         </is>
@@ -814,36 +808,36 @@
           <t>09-30</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="6" t="n">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="7" t="n">
         <v>4500</v>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>FY25 (FYE 9/30/25): Caltech Endowment Report, 9.9% return, $4.5B. Caltech FYE = Sept 30, not June 30; true FY26 just closed 9/30/26, not yet reported.</t>
         </is>
@@ -868,28 +862,28 @@
           <t>08-31</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="5" t="n">
         <v>31.7</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>10.3</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="5" t="n">
         <v>12.5</v>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="6" t="n">
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="7" t="n">
         <v>40800</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="7" t="n">
         <v>61500</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>FY26: Stanford Report (Sept 2026), 31.7% return, Merged Pool $61.5B as of 8/31/26 (Stanford FYE = Aug 31, not June 30). FY25 return 14.3%. FY26 5-yr annualized 10.3%, 10-yr annualized 12.5% (Stanford Report, Sept 2026).</t>
         </is>
@@ -914,32 +908,32 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="5" t="n">
         <v>27.4</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="6" t="n">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="7" t="n">
         <v>24800</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="7" t="n">
         <v>31100</v>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>FY26: Daily Pennsylvanian (Sept 24, 2026), 27.4% return, $24.8B→$31.1B, largest single-year gain on record.</t>
         </is>
@@ -964,36 +958,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="6" t="n">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="7" t="n">
         <v>12300</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>FY25: P&amp;I, 9% FY25 return, $12.3B (NACUBO-style). FY26 not yet released.</t>
         </is>
@@ -1018,36 +1012,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="6" t="n">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="7" t="n">
         <v>13700</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>FY25: Forbes/NACUBO-style compilation, $13.7B. No official return % disclosed by JHU. FY26 not yet released.</t>
         </is>
@@ -1072,36 +1066,36 @@
           <t>08-31</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="6" t="n">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="7" t="n">
         <v>15300</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>FY25: Northwestern financial update (Jan 2026), 11.3% return (12mo to 6/30/25), $15.3B as of 8/31/25. FY26 not yet released.</t>
         </is>
@@ -1126,36 +1120,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="6" t="n">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="7" t="n">
         <v>10900</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>FY25: P&amp;I/CIO (Oct 2025), 10.2% FY25 return, $10.9B. FY26 not yet released.</t>
         </is>
@@ -1180,36 +1174,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="6" t="n">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="7" t="n">
         <v>15900</v>
       </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>FY25: Columbia IMC, 12.4% return, $15.9B. FY26 not yet released.</t>
         </is>
@@ -1234,36 +1228,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="6" t="n">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="7" t="n">
         <v>9000</v>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>FY25: AI-CIO, 10.8% return, $9.0B. FY26 not yet released.</t>
         </is>
@@ -1288,36 +1282,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="6" t="n">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="7" t="n">
         <v>3484</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>FY25: CMU Annual Report, 10.9% return, $3.484B. FY26 not yet released.</t>
         </is>
@@ -1342,36 +1336,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="6" t="n">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="7" t="n">
         <v>11800</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>FY25: Cornell Statements (Oct 2025), 12.3% return, $11.8B. FY26 not yet released.</t>
         </is>
@@ -1396,36 +1390,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="6" t="n">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="7" t="n">
         <v>8000</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>FY25: Brown Univ. (Oct 2025), 11.9% return, $8.0B. FY26 not yet released.</t>
         </is>
@@ -1450,36 +1444,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="6" t="n">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="7" t="n">
         <v>8500</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t>FY25: Rice Mgmt Co. report, 11.4% return, $8.5B total endowment ($7.9B investment pool). FY26 not yet released.</t>
         </is>
@@ -1504,36 +1498,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="6" t="n">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="7" t="n">
         <v>10900</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>FY25: Vanderbilt Hustler (Dec 2025), 9.9% return, $10.9B. FY26 not yet released.</t>
         </is>
@@ -1558,36 +1552,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="5" t="n">
         <v>37.3</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>18.65</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>13400</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>FY26: Bloomberg (Sept 25, 2026), 37.3% return driven by legacy SpaceX stake. FY26 dollar value not yet disclosed; FY25 value ($13.4B) is estimated.</t>
         </is>
@@ -1612,36 +1606,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="6" t="n">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="7" t="n">
         <v>3390</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>UC Berkeley Foundation FY25: P&amp;I, 10.0% return, $3.39B (campus foundation, not UC system-wide pool). FY26 not yet released.</t>
         </is>
@@ -1666,36 +1660,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="6" t="n">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="7" t="n">
         <v>4770</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t>UCLA Foundation FY25: P&amp;I, 11.6% return, $4.77B (campus foundation, not UC system-wide pool). FY26 not yet released.</t>
         </is>
@@ -1720,36 +1714,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="6" t="n">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="7" t="n">
         <v>25400</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>FY25: Notre Dame Annual Report, 13.6% return, $25.4B. FY26 not yet released.</t>
         </is>
@@ -1774,36 +1768,36 @@
           <t>08-31</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="6" t="n">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="7" t="n">
         <v>8930</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
         <is>
           <t>FY25 (FYE 8/31/25): Emory audit report, $8.93B. No official % return disclosed by Emory. FY26 (FYE 8/31/26) closed but not yet reported.</t>
         </is>
@@ -1828,38 +1822,38 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>No reliable primary-source FY25 dollar figure or return % located (~$4B cited generally in 2025 CIO-hire coverage).</t>
         </is>
@@ -1884,36 +1878,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="6" t="n">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="7" t="n">
         <v>21200</v>
       </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>FY25: The University Record (Oct 2025), 15.5% return, $21.2B. FY26 not yet released.</t>
         </is>
@@ -1938,30 +1932,30 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="n">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="6" t="n">
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="7" t="n">
         <v>15500</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="7" t="n">
         <v>18800</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>FY26: Cavalier Daily (Sept 19, 2026), UVIMCO 27% return vs. 9.8% benchmark, $15.5B→$18.8B. 10-yr annualized approximately 12% ('approximately 12 percent annually' over the past 10 years), per UVIMCO CEO/CIO Robert Durden at the Sept 2026 Finance Committee meeting (Cavalier Daily); stated as an approximate figure, not to a decimal. No FY26 5-yr figure reported yet.</t>
         </is>
@@ -1986,30 +1980,30 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="5" t="n">
         <v>12.5</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="5" t="n">
         <v>13.5</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="7" t="n">
         <v>12500</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="7" t="n">
         <v>17000</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t>FY26: Bloomberg (Sept 19, 2026), 37.8% return, UNC Investment Fund $12.5B→$17.0B, driven by legacy SpaceX stake (about half of FY26 growth, per UNC Management Company president Stefan Strein). (UNC-CH Foundation portion: $6.04B→$8.16B.) 5-yr annualized 12.5%, 10-yr annualized 13.5% (Bloomberg/WRAL/Investing.com/Hoodline, Sept 19-22, 2026).</t>
         </is>
@@ -2034,36 +2028,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="6" t="n">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="7" t="n">
         <v>9030</v>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t>FY25: USC Endowment Report, 14.0% return, $9.03B. FY26 not yet released.</t>
         </is>
@@ -2088,36 +2082,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="6" t="n">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>Georgia Tech Foundation FY25: P&amp;I, 11.1% return, ~$3B. FY26 not yet released.</t>
         </is>
@@ -2142,36 +2136,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="6" t="n">
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="7" t="n">
         <v>1770</v>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>UC San Diego Foundation FY25 audited financials, 13.0% return, ~$1.75-1.79B. FY26 not yet released.</t>
         </is>
@@ -2196,38 +2190,38 @@
           <t>05-31</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>FY25 return ~12% (Boston Globe); standalone audited FY25 dollar value not confirmed. FY26 not yet released.</t>
         </is>
@@ -2252,36 +2246,36 @@
           <t>08-31</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="6" t="n">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="7" t="n">
         <v>6000</v>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>FY25 value ~$6B per third-party AUM tracker (unconfirmed vs. primary source). FY26 not yet released.</t>
         </is>
@@ -2306,36 +2300,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="6" t="n">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>FY25: P&amp;I, 10% return; dollar value ~$3B AUM unconfirmed vs. primary source. FY26 not yet released.</t>
         </is>
@@ -2360,36 +2354,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="6" t="n">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="7" t="n">
         <v>4046</v>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
         <is>
           <t>FY25: BU Consolidated Financial Report, 14.8% return (P&amp;I), $4.046B (audited). FY26 not yet released.</t>
         </is>
@@ -2414,36 +2408,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="6" t="n">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>UC system pool ~$1.8B at 6/30/25; UC GEP-wide FY25 return 12.2%. FY26 not yet released.</t>
         </is>
@@ -2468,36 +2462,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="6" t="n">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="7" t="n">
         <v>650</v>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
         <is>
           <t>UC system pool ~$650M at 6/30/25 (GEP FY25 +12.2%); separate UC Irvine Foundation ~$1B, 11.2% FY25 return. FY26 not yet released.</t>
         </is>
@@ -2522,38 +2516,38 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t>UF Foundation/UFICO FY25 return 12.1% (P&amp;I); FY25 dollar value not confirmed from primary source. FY26 not yet released.</t>
         </is>
@@ -2578,36 +2572,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="6" t="n">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="7" t="n">
         <v>3060</v>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
         <is>
           <t>University of Illinois Foundation FY25: $3.06B, 3.3% return (notably below benchmark). FY26 not yet released.</t>
         </is>
@@ -2632,38 +2626,38 @@
           <t>08-31</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
         <is>
           <t>UTIMCO (PUF/GEF, FYE Aug 31) FY25 return 10% (P&amp;I); dollar value not confirmed. FY26 (FYE 8/31/26) not yet released.</t>
         </is>
@@ -2688,36 +2682,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="6" t="n">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="7" t="n">
         <v>4900</v>
       </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
         <is>
           <t>WFAA FY25 return cited as exceeding 16%; ~$4.9B in endowed funds (dollar figure unconfirmed vs. primary source). FY26 not yet released.</t>
         </is>
@@ -2742,36 +2736,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="6" t="n">
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="7" t="n">
         <v>2150</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
         <is>
           <t>New to top 50 in 2027 US News edition. FY25 (FYE 6/30/25): Wake Forest Consolidated Financial Statements, $2.150B combined (Reynolda Campus $1,235.8M + WFUHS $913.9M). No officially stated FY25/FY26 return % disclosed (statements report investment gains in dollar terms only). FY26 not yet released.</t>
         </is>
@@ -2820,7 +2814,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
@@ -2848,36 +2842,36 @@
           <t>05-31</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="6" t="n">
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="7" t="n">
         <v>1415</v>
       </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
         <is>
           <t>New to top 50 in 2027 US News edition. FY25 (FYE 5/31/25, Villanova's fiscal year runs June-May): Villanova Financial Statements, $1.415B (up from $1.313B in FY24). No officially stated return % disclosed. FY26 (ending 5/31/26) not yet released.</t>
         </is>
@@ -2902,36 +2896,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="6" t="n">
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="7" t="n">
         <v>2500</v>
       </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
         <is>
           <t>New to top 50 in 2027 US News edition. FY25 (FYE 6/30/25): CWRU Endowment Report / Pensions &amp; Investments, ~$2.5B, 8.53% FY25 return (vs 9.58% policy benchmark) — this is the FY25 return, not FY26. FY26 not yet released.</t>
         </is>
@@ -2956,36 +2950,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="6" t="n">
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
         <is>
           <t>FY25: P&amp;I, 10.4% return, ~$2.00B (NACUBO-style, unconfirmed vs. primary source). FY26 not yet released.</t>
         </is>
@@ -3010,36 +3004,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="6" t="n">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="7" t="n">
         <v>2058</v>
       </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
         <is>
           <t>Rutgers Finance &amp; Admin, ~$2.058B (latest published, may be FY24). FY26 not yet released.</t>
         </is>
@@ -3064,36 +3058,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="6" t="n">
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="7" t="n">
         <v>8620</v>
       </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
         <is>
           <t>FY25: NACUBO-TIAA study / P&amp;I, 11.8% return, $8.62B (not independently confirmed vs. OSU's own statements). FY26 not yet released.</t>
         </is>
@@ -3118,36 +3112,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="6" t="n">
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="7" t="n">
         <v>285</v>
       </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
         <is>
           <t>UC system pool only, ~$285.4M at 6/30/25 (GEP FY25 +12.2%); UCSB Foundation assets not confirmed separately. FY26 not yet released.</t>
         </is>
@@ -3172,36 +3166,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="6" t="n">
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="7" t="n">
         <v>1240</v>
       </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L50" s="7" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
         <is>
           <t>UMCP Foundation FY25 Endowment Report: $1.24B, +8.2% return (below 10.9% benchmark). FY26 not yet released.</t>
         </is>
@@ -3226,36 +3220,36 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="6" t="n">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="7" t="n">
         <v>3800</v>
       </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
         <is>
           <t>FY25 Endowment Report (unaudited): $3.8B, 12.0% net return. FY26 not yet released.</t>
         </is>
@@ -3280,38 +3274,38 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
         <is>
           <t>FY25 return 12.4% (P&amp;I); dollar figure not independently confirmed. FY26 not yet released.</t>
         </is>
@@ -3359,7 +3353,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>As of 2026-09-28: 6 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), University of Virginia (27.0%), Northeastern University (16.0%, management estimate). 5-year annualized: 2 of 51. 10-year annualized: 3 of 51.</t>
+          <t>As of 2026-10-02: 7 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), University of Virginia (27.0%), Northeastern University (16.0%, management estimate), Massachusetts Institute of Technology (10.3%). 5-year annualized: 2 of 51. 10-year annualized: 4 of 51.</t>
         </is>
       </c>
     </row>

--- a/endowment/output/FY26_Endowment_Data_Top50.xlsx
+++ b/endowment/output/FY26_Endowment_Data_Top50.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -1390,38 +1390,30 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="E17" s="5" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>13.6</v>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="7" t="n">
         <v>8000</v>
       </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J17" s="7" t="n">
+        <v>9500</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>FY25: Brown Univ. (Oct 2025), 11.9% return, $8.0B. FY26 not yet released.</t>
+          <t>FY25: Brown Univ. (Oct 2025), 11.9% return, $8.0B. FY26 not yet released. FY26: Brown Univ. news (Oct 9, 2026): 19.6% 1-yr, 7.8% 5-yr, 13.6% 10-yr annualized; endowment rose from $8B to $9.5B (rounded, per release).</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1462,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -1524,7 +1516,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -1632,7 +1624,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -1686,7 +1678,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
@@ -1740,7 +1732,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -1794,7 +1786,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
@@ -1850,7 +1842,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -1904,7 +1896,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -1952,7 +1944,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -2000,7 +1992,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
@@ -2054,7 +2046,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
@@ -2108,7 +2100,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -2162,7 +2154,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -2218,7 +2210,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
@@ -2272,7 +2264,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2326,7 +2318,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -2380,7 +2372,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -2434,7 +2426,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -2488,7 +2480,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -2544,7 +2536,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
@@ -2598,7 +2590,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
@@ -2654,7 +2646,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
@@ -2708,7 +2700,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -2762,7 +2754,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
@@ -2814,7 +2806,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
@@ -2868,7 +2860,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
@@ -2922,7 +2914,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
@@ -2976,7 +2968,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
@@ -3030,7 +3022,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
@@ -3058,15 +3050,11 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>9.17</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -3077,19 +3065,17 @@
       <c r="I48" s="7" t="n">
         <v>8620</v>
       </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J48" s="7" t="n">
+        <v>9700</v>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>FY25: NACUBO-TIAA study / P&amp;I, 11.8% return, $8.62B (not independently confirmed vs. OSU's own statements). FY26 not yet released.</t>
+          <t>FY25: NACUBO-TIAA study / P&amp;I, 11.8% return, $8.62B (not independently confirmed vs. OSU's own statements). FY26 not yet released. FY26: OSU Business &amp; Finance investments page (busfin.osu.edu/investments), Long-Term Investment Pool 16.03% (benchmark 17.08%, preliminary), 5-yr 9.17%; pool $9.7B at 6/30/26 (LTIP, not full endowment). 10-yr not stated.</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3124,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -3192,7 +3178,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
@@ -3246,7 +3232,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
@@ -3302,7 +3288,7 @@
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
@@ -3353,7 +3339,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>As of 2026-10-02: 7 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), University of Virginia (27.0%), Northeastern University (16.0%, management estimate), Massachusetts Institute of Technology (10.3%). 5-year annualized: 2 of 51. 10-year annualized: 4 of 51.</t>
+          <t>As of 2026-10-09: 9 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), University of Virginia (27.0%), Brown University (19.6%), The Ohio State University (16.0%), Northeastern University (16.0%, management estimate), Massachusetts Institute of Technology (10.3%). 5-year annualized: 4 of 51. 10-year annualized: 5 of 51.</t>
         </is>
       </c>
     </row>

--- a/endowment/output/FY26_Endowment_Data_Top50.xlsx
+++ b/endowment/output/FY26_Endowment_Data_Top50.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -700,10 +700,8 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="E4" s="5" t="n">
+        <v>27.1</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -719,19 +717,17 @@
       <c r="I4" s="7" t="n">
         <v>56900</v>
       </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J4" s="7" t="n">
+        <v>68000</v>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>FY25: Harvard Magazine (Oct 2025), 11.9% FY25 return, $56.9B. FY26 not yet released.</t>
+          <t>FY26: Harvard Magazine and AI-CIO (Oct 15, 2026) citing Harvard Management Company, 27.1% net of investment expenses, ~$68B at June 30, 2026 (from $56.9B). 5- and 10-yr not stated. No source attributes a specific share of the return to SpaceX, so spacexPts left null. FY25: Harvard Magazine (Oct 2025), 11.9%, $56.9B.</t>
         </is>
       </c>
     </row>
@@ -780,7 +776,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -834,7 +830,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -930,7 +926,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -984,7 +980,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1038,7 +1034,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -1146,7 +1142,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -1200,7 +1196,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -1254,7 +1250,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
@@ -1308,7 +1304,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
@@ -1362,7 +1358,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -1408,7 +1404,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
@@ -1462,7 +1458,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -1516,7 +1512,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -1570,7 +1566,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -1624,7 +1620,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -1678,7 +1674,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
@@ -1732,7 +1728,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -1786,7 +1782,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
@@ -1842,7 +1838,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -1896,7 +1892,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -1944,7 +1940,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -1992,7 +1988,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
@@ -2046,7 +2042,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
@@ -2100,7 +2096,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -2154,7 +2150,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -2210,7 +2206,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
@@ -2264,7 +2260,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2318,7 +2314,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -2372,7 +2368,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -2426,7 +2422,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -2480,7 +2476,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -2536,7 +2532,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
@@ -2590,7 +2586,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
@@ -2646,7 +2642,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
@@ -2700,7 +2696,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -2754,7 +2750,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
@@ -2806,7 +2802,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
@@ -2860,7 +2856,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
@@ -2914,7 +2910,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
@@ -2968,7 +2964,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
@@ -3022,7 +3018,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
@@ -3070,7 +3066,7 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
@@ -3124,7 +3120,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -3178,7 +3174,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
@@ -3232,7 +3228,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
@@ -3288,7 +3284,7 @@
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
@@ -3339,7 +3335,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>As of 2026-10-09: 9 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), University of Virginia (27.0%), Brown University (19.6%), The Ohio State University (16.0%), Northeastern University (16.0%, management estimate), Massachusetts Institute of Technology (10.3%). 5-year annualized: 4 of 51. 10-year annualized: 5 of 51.</t>
+          <t>As of 2026-10-16: 10 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), Harvard University (27.1%), University of Virginia (27.0%), Brown University (19.6%), The Ohio State University (16.0%), Northeastern University (16.0%, management estimate), Massachusetts Institute of Technology (10.3%). 5-year annualized: 4 of 51. 10-year annualized: 5 of 51.</t>
         </is>
       </c>
     </row>

--- a/endowment/output/FY26_Endowment_Data_Top50.xlsx
+++ b/endowment/output/FY26_Endowment_Data_Top50.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -646,10 +646,8 @@
           <t>06-30</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="E3" s="5" t="n">
+        <v>23.7</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
@@ -665,19 +663,17 @@
       <c r="I3" s="7" t="n">
         <v>36400</v>
       </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="J3" s="7" t="n">
+        <v>42300</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>FY25: Princeton Alumni Weekly (Oct 2025), 11% FY25 return, $36.4B. FY26 not yet released.</t>
+          <t>FY25: Princeton Alumni Weekly (Oct 2025), 11% FY25 return, $36.4B. FY26: AI-CIO (Oct 20, 2026), 23.7% return, endowment $42.3B (press figure, from $36.4B). 5-yr/10-yr not recorded: AI-CIO cites 6.7%/11% without labeling them annualized and another outlet cites 11.3% for ten years, so left null pending primary source. No SpaceX attribution quantified.</t>
         </is>
       </c>
     </row>
@@ -722,7 +718,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -776,7 +772,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -830,7 +826,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -926,7 +922,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -980,7 +976,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1034,7 +1030,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -1088,7 +1084,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -1142,7 +1138,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
@@ -1304,7 +1300,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
@@ -1358,7 +1354,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -1458,7 +1454,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -1512,7 +1508,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -1566,7 +1562,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -1620,7 +1616,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -1674,7 +1670,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
@@ -1728,7 +1724,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
@@ -1782,7 +1778,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
@@ -1838,7 +1834,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -1892,7 +1888,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -1940,7 +1936,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -2042,7 +2038,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
@@ -2096,7 +2092,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -2150,7 +2146,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -2206,7 +2202,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
@@ -2260,7 +2256,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2314,7 +2310,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -2368,7 +2364,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -2422,7 +2418,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -2476,7 +2472,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -2532,7 +2528,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
@@ -2586,7 +2582,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
@@ -2642,7 +2638,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
@@ -2696,7 +2692,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -2750,7 +2746,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
@@ -2802,7 +2798,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
@@ -2856,7 +2852,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
@@ -2910,7 +2906,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
@@ -2964,7 +2960,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
@@ -3018,7 +3014,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
@@ -3066,7 +3062,7 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
@@ -3120,7 +3116,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -3174,7 +3170,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
@@ -3228,7 +3224,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
@@ -3284,7 +3280,7 @@
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
@@ -3335,7 +3331,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>As of 2026-10-16: 10 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), Harvard University (27.1%), University of Virginia (27.0%), Brown University (19.6%), The Ohio State University (16.0%), Northeastern University (16.0%, management estimate), Massachusetts Institute of Technology (10.3%). 5-year annualized: 4 of 51. 10-year annualized: 5 of 51.</t>
+          <t>As of 2026-10-23: 11 of 51 institutions had released an FY26 1-year return: University of North Carolina at Chapel Hill (37.8%), Washington University in St. Louis (37.3%), Stanford University (31.7%), University of Pennsylvania (27.4%), Harvard University (27.1%), University of Virginia (27.0%), Princeton University (23.7%), Brown University (19.6%), The Ohio State University (16.0%), Northeastern University (16.0%, management estimate), Massachusetts Institute of Technology (10.3%). 5-year annualized: 4 of 51. 10-year annualized: 5 of 51.</t>
         </is>
       </c>
     </row>
